--- a/lenguaje/mia07_t3_tra_resultados_viterbi.xlsx
+++ b/lenguaje/mia07_t3_tra_resultados_viterbi.xlsx
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AQ0MS0</t>
+          <t>NCFS000</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -486,7 +486,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1.295582484193506e-09</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -504,14 +504,14 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SPS00</t>
+          <t>VMIP3S0</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.0012941074971961</v>
       </c>
       <c r="C3" t="n">
-        <v>1.988063133517315e-05</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -523,7 +523,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>5.440257583147429e-12</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -535,7 +535,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>NCMP000</t>
+          <t>Fp</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -557,16 +557,16 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.107075865754602e-15</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>3.529518322132861e-16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DA0MS0</t>
+          <t>NCMP000</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2.779888150251198e-06</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -588,7 +588,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4.107075865754602e-15</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -597,14 +597,14 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Fp</t>
+          <t>SPS00</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1.988063133517315e-05</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -616,13 +616,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>5.440257583147429e-12</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3.529518322132861e-16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -659,7 +659,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>NCFS000</t>
+          <t>DA0MS0</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -669,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2.779888150251198e-06</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -721,11 +721,11 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>VMIP3S0</t>
+          <t>AQ0MS0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0012941074971961</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -734,7 +734,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1.295582484193506e-09</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
